--- a/data/信用债发行汇总_2026-08-06.xlsx
+++ b/data/信用债发行汇总_2026-08-06.xlsx
@@ -891,7 +891,11 @@
           <t>26西安高新MTN008A</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr"/>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>102682951.IB</t>
+        </is>
+      </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
           <t>3Y</t>
@@ -1050,7 +1054,11 @@
           <t>26华发集团SCP006</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr"/>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>012681978.IB</t>
+        </is>
+      </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
           <t>0.73Y</t>
@@ -1217,7 +1225,11 @@
           <t>26西安高新MTN008B</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr"/>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>102682952.IB</t>
+        </is>
+      </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
           <t>5Y</t>
@@ -1376,7 +1388,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN23"/>
+  <dimension ref="A1:AN24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1815,7 +1827,11 @@
           <t>26西安高新MTN008A</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr"/>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>102682951.IB</t>
+        </is>
+      </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
           <t>3Y</t>
@@ -1979,7 +1995,11 @@
           <t>26华发集团SCP006</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr"/>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>012681978.IB</t>
+        </is>
+      </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>0.73Y</t>
@@ -2151,7 +2171,11 @@
           <t>26西安高新MTN008B</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr"/>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>102682952.IB</t>
+        </is>
+      </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
           <t>5Y</t>
@@ -2474,68 +2498,68 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>08-03 18:00</t>
+          <t>08-05 18:00</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>26农业银行绿色债01</t>
+          <t>26浙商银行永续债01BC</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>2628001.IB</t>
+          <t>242680031.IB</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5+N</t>
         </is>
       </c>
       <c r="F7" s="2" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1.20 ~ 1.80</t>
+          <t>1.65 ~ 2.25</t>
         </is>
       </c>
       <c r="H7" s="4" t="n">
-        <v>1.51</v>
+        <v>1.95</v>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>中国农业银行股份有限公司</t>
+          <t>浙商银行股份有限公司</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>浙江省-杭州市</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>25农业银行绿色债02</t>
+          <t>21浙商银行永续债</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3.57Y</t>
+          <t>113D+N</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1.5338</t>
+          <t>1.4867</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -2550,18 +2574,18 @@
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,中国国际金融股份有限公司,中信建投证券股份有限公司,华泰证券股份有限公司,招商证券股份有限公司,中银国际证券股份有限公司,国投证券股份有限公司,中国银河证券股份有限公司,申万宏源证券有限公司,国泰海通证券股份有限公司</t>
+          <t>中信证券股份有限公司,国泰海通证券股份有限公司,中国工商银行股份有限公司,中国银行股份有限公司,中国邮政储蓄银行股份有限公司,中国民生银行股份有限公司,平安银行股份有限公司,兴业银行股份有限公司,上海浦东发展银行股份有限公司,北京银行股份有限公司,江苏银行股份有限公司,中银国际证券股份有限公司,中信建投证券股份有限公司,中国银河证券股份有限公司,国投证券股份有限公司,申万宏源证券有限公司,中国国际金融股份有限公司,光大证券股份有限公司,东方证券股份有限公司</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr"/>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>商业银行普通债券</t>
+          <t>商业银行次级债券</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>中央国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2571,7 +2595,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>中国农业银行股份有限公司2026年绿色金融债券(第一期)(债券通)</t>
+          <t>浙商银行股份有限公司2026年无固定期限资本债券(第一期)(债券通)</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -2581,23 +2605,19 @@
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>2029-08-05</t>
-        </is>
-      </c>
-      <c r="Y7" s="2" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2031-08-07</t>
+        </is>
+      </c>
+      <c r="Y7" s="2" t="inlineStr"/>
       <c r="Z7" s="2" t="inlineStr"/>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -2607,7 +2627,7 @@
       </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AE7" s="2" t="inlineStr">
@@ -2622,7 +2642,7 @@
       </c>
       <c r="AG7" s="2" t="inlineStr">
         <is>
-          <t>国有银行</t>
+          <t>股份制银行</t>
         </is>
       </c>
       <c r="AH7" s="2" t="inlineStr">
@@ -2638,17 +2658,17 @@
       </c>
       <c r="AK7" s="2" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AL7" s="2" t="inlineStr">
         <is>
-          <t>普通债权</t>
+          <t>其他一级资本工具</t>
         </is>
       </c>
       <c r="AM7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AN7" s="2" t="inlineStr"/>
@@ -2656,22 +2676,22 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>07-29 16:30</t>
+          <t>08-03 18:00</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>26湖南银行债01</t>
+          <t>26农业银行绿色债01</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>212680010.IB</t>
+          <t>2628001.IB</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -2680,44 +2700,44 @@
         </is>
       </c>
       <c r="F8" s="2" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.80</t>
+          <t>1.20 ~ 1.80</t>
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>1.59</v>
+        <v>1.51</v>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>湖南银行股份有限公司</t>
+          <t>中国农业银行股份有限公司</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>湖南省-长沙市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>25湖南银行债01</t>
+          <t>25农业银行绿色债02</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2.02Y</t>
+          <t>3.57Y</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1.5812</t>
+          <t>1.5338</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -2732,7 +2752,7 @@
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>中国国际金融股份有限公司,中信证券股份有限公司,中信建投证券股份有限公司,国泰海通证券股份有限公司,申万宏源证券有限公司,东方证券股份有限公司,中国银行股份有限公司,兴业银行股份有限公司,华夏银行股份有限公司,恒丰银行股份有限公司</t>
+          <t>中信证券股份有限公司,中国国际金融股份有限公司,中信建投证券股份有限公司,华泰证券股份有限公司,招商证券股份有限公司,中银国际证券股份有限公司,国投证券股份有限公司,中国银河证券股份有限公司,申万宏源证券有限公司,国泰海通证券股份有限公司</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr"/>
@@ -2743,7 +2763,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>中央国有企业</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2753,7 +2773,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>湖南银行股份有限公司2026年第一期金融债券</t>
+          <t>中国农业银行股份有限公司2026年绿色金融债券(第一期)(债券通)</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -2763,19 +2783,23 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>2029-07-31</t>
-        </is>
-      </c>
-      <c r="Y8" s="2" t="inlineStr"/>
+          <t>2029-08-05</t>
+        </is>
+      </c>
+      <c r="Y8" s="2" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="Z8" s="2" t="inlineStr"/>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -2785,7 +2809,7 @@
       </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE8" s="2" t="inlineStr">
@@ -2800,7 +2824,7 @@
       </c>
       <c r="AG8" s="2" t="inlineStr">
         <is>
-          <t>城商行</t>
+          <t>国有银行</t>
         </is>
       </c>
       <c r="AH8" s="2" t="inlineStr">
@@ -2826,7 +2850,7 @@
       </c>
       <c r="AM8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="AN8" s="2" t="inlineStr"/>
@@ -2834,89 +2858,89 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>07-27 19:00</t>
+          <t>07-29 16:30</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>26鸿飞02</t>
+          <t>26湖南银行债01</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>283448.SH</t>
+          <t>212680010.IB</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="F9" s="2" t="n">
-        <v>5</v>
+        <v>70</v>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2.00 ~ 3.00</t>
+          <t>1.30 ~ 1.80</t>
         </is>
       </c>
       <c r="H9" s="4" t="n">
-        <v>2.34</v>
+        <v>1.59</v>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>江油鸿飞投资(集团)有限公司</t>
+          <t>湖南银行股份有限公司</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>四川省-绵阳市</t>
+          <t>湖南省-长沙市</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>26鸿飞01</t>
+          <t>25湖南银行债01</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4.67Y</t>
+          <t>2.02Y</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2.2945</t>
+          <t>1.5812</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>长城证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>四川省金玉融资担保有限公司</t>
-        </is>
-      </c>
+          <t>中国国际金融股份有限公司,中信证券股份有限公司,中信建投证券股份有限公司,国泰海通证券股份有限公司,申万宏源证券有限公司,东方证券股份有限公司,中国银行股份有限公司,兴业银行股份有限公司,华夏银行股份有限公司,恒丰银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr"/>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>商业银行普通债券</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
@@ -2926,70 +2950,70 @@
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>江油鸿飞投资(集团)有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>湖南银行股份有限公司2026年第一期金融债券</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>2031-07-28</t>
+          <t>2029-07-31</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr"/>
       <c r="Z9" s="2" t="inlineStr"/>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AE9" s="2" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AF9" s="2" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>商业银行</t>
         </is>
       </c>
       <c r="AG9" s="2" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城商行</t>
         </is>
       </c>
       <c r="AH9" s="2" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AI9" s="2" t="inlineStr"/>
       <c r="AJ9" s="2" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AK9" s="2" t="inlineStr">
@@ -3004,7 +3028,7 @@
       </c>
       <c r="AM9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AN9" s="2" t="inlineStr"/>
@@ -3012,82 +3036,86 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>07-23 19:00</t>
+          <t>07-27 19:00</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>26长开G1</t>
+          <t>26鸿飞02</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>245671.SH</t>
+          <t>283448.SH</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
+          <t>2.00 ~ 3.00</t>
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>1.7</v>
+        <v>2.34</v>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>重庆长寿开发投资(集团)有限公司</t>
+          <t>江油鸿飞投资(集团)有限公司</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>重庆市-长寿区</t>
+          <t>四川省-绵阳市</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>24长寿开投MTN003A</t>
+          <t>26鸿飞01</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1.10Y+2.00Y</t>
+          <t>4.67Y</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1.7196</t>
+          <t>2.2945</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>7-</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr"/>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>国投证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr"/>
+          <t>长城证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>四川省金玉融资担保有限公司</t>
+        </is>
+      </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -3105,29 +3133,29 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>重庆长寿开发投资(集团)有限公司2026年面向专业投资者公开发行公司债券(第一期)</t>
+          <t>江油鸿飞投资(集团)有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>2027-07-28</t>
+          <t>2031-07-28</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr"/>
       <c r="Z10" s="2" t="inlineStr"/>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -3137,22 +3165,22 @@
       </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AE10" s="2" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AF10" s="2" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AG10" s="2" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AH10" s="2" t="inlineStr">
@@ -3163,7 +3191,7 @@
       <c r="AI10" s="2" t="inlineStr"/>
       <c r="AJ10" s="2" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AK10" s="2" t="inlineStr">
@@ -3178,7 +3206,7 @@
       </c>
       <c r="AM10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AN10" s="2" t="inlineStr"/>
@@ -3191,84 +3219,80 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>07-23 18:00</t>
+          <t>07-23 19:00</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>26恒丰银行绿债01B</t>
+          <t>26长开G1</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>222680007.IB</t>
+          <t>245671.SH</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>1Y</t>
         </is>
       </c>
       <c r="F11" s="2" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1.35 ~ 1.85</t>
+          <t>1.40 ~ 2.40</t>
         </is>
       </c>
       <c r="H11" s="4" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>恒丰银行股份有限公司</t>
+          <t>重庆长寿开发投资(集团)有限公司</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>山东省-济南市</t>
+          <t>重庆市-长寿区</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>25恒丰银行债02</t>
+          <t>24长寿开投MTN003A</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1.83Y</t>
+          <t>1.10Y+2.00Y</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1.5832</t>
+          <t>1.7196</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4-</t>
+          <t>7</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr"/>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>中国国际金融股份有限公司,国泰海通证券股份有限公司,东方证券股份有限公司,申万宏源证券有限公司,德邦证券股份有限公司,中国进出口银行,中国银行股份有限公司,中国建设银行股份有限公司,兴业银行股份有限公司</t>
+          <t>国投证券股份有限公司</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr"/>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>商业银行普通债券</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -3278,12 +3302,12 @@
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>恒丰银行股份有限公司2026年第一期绿色金融债券(品种二)</t>
+          <t>重庆长寿开发投资(集团)有限公司2026年面向专业投资者公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3293,14 +3317,14 @@
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>2029-07-27</t>
+          <t>2027-07-28</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr"/>
       <c r="Z11" s="2" t="inlineStr"/>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
@@ -3310,32 +3334,32 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AE11" s="2" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AF11" s="2" t="inlineStr">
         <is>
-          <t>商业银行</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AG11" s="2" t="inlineStr">
         <is>
-          <t>股份制银行</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AH11" s="2" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AI11" s="2" t="inlineStr"/>
@@ -3374,12 +3398,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>26恒丰银行绿债01A</t>
+          <t>26恒丰银行绿债01B</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>222680006.IB</t>
+          <t>222680007.IB</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -3388,15 +3412,15 @@
         </is>
       </c>
       <c r="F12" s="2" t="n">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.80</t>
+          <t>1.35 ~ 1.85</t>
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
@@ -3461,7 +3485,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>恒丰银行股份有限公司2026年第一期绿色金融债券(品种一)</t>
+          <t>恒丰银行股份有限公司2026年第一期绿色金融债券(品种二)</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -3552,75 +3576,79 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>26成都开投PPN001</t>
+          <t>26恒丰银行绿债01A</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>032601649.IB</t>
+          <t>222680006.IB</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5+5</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="F13" s="2" t="n">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.80</t>
+          <t>1.30 ~ 1.80</t>
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>2.25</v>
+        <v>1.56</v>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>成都经开国投集团有限公司</t>
+          <t>恒丰银行股份有限公司</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>四川省-成都市</t>
+          <t>山东省-济南市</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>25成都开投PPN002</t>
+          <t>25恒丰银行债02</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4.31Y+5.00Y</t>
+          <t>1.83Y</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2.1942</t>
+          <t>1.5832</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4-</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>广发证券股份有限公司,成都银行股份有限公司,国投证券股份有限公司</t>
+          <t>中国国际金融股份有限公司,国泰海通证券股份有限公司,东方证券股份有限公司,申万宏源证券有限公司,德邦证券股份有限公司,中国进出口银行,中国银行股份有限公司,中国建设银行股份有限公司,兴业银行股份有限公司</t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr"/>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>商业银行普通债券</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
@@ -3635,70 +3663,62 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>成都经开国投集团有限公司2026年度第一期定向债务融资工具</t>
+          <t>恒丰银行股份有限公司2026年第一期绿色金融债券(品种一)</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>2036-07-24</t>
+          <t>2029-07-27</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr"/>
-      <c r="Z13" s="2" t="inlineStr">
+      <c r="Z13" s="2" t="inlineStr"/>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
         <is>
           <t>2026-07-27</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB13" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE13" s="2" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AF13" s="2" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>商业银行</t>
         </is>
       </c>
       <c r="AG13" s="2" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>股份制银行</t>
         </is>
       </c>
       <c r="AH13" s="2" t="inlineStr">
         <is>
-          <t>房屋建设</t>
-        </is>
-      </c>
-      <c r="AI13" s="2" t="inlineStr">
-        <is>
-          <t>2031-07-24</t>
-        </is>
-      </c>
+          <t>银行</t>
+        </is>
+      </c>
+      <c r="AI13" s="2" t="inlineStr"/>
       <c r="AJ13" s="2" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -3706,7 +3726,7 @@
       </c>
       <c r="AK13" s="2" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AL13" s="2" t="inlineStr">
@@ -3719,92 +3739,90 @@
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="AN13" s="2" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AN13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>07-17 18:00</t>
+          <t>07-23 18:00</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>26云能MTN004</t>
+          <t>26成都开投PPN001</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>102682656.IB</t>
+          <t>032601649.IB</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>5+5</t>
         </is>
       </c>
       <c r="F14" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.40</t>
+          <t>1.80 ~ 2.80</t>
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>云南省能源集团有限公司</t>
+          <t>成都经开国投集团有限公司</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>云南省</t>
+          <t>四川省-成都市</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>24云能投GN001</t>
+          <t>25成都开投PPN002</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4.93Y</t>
+          <t>4.31Y+5.00Y</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2.2567</t>
+          <t>2.1942</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr"/>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>中国银行股份有限公司,广发证券股份有限公司</t>
+          <t>广发证券股份有限公司,成都银行股份有限公司,国投证券股份有限公司</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr"/>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -3819,70 +3837,70 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>云南省能源集团有限公司2026年度第四期中期票据</t>
+          <t>成都经开国投集团有限公司2026年度第一期定向债务融资工具</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>2031-07-20</t>
-        </is>
-      </c>
-      <c r="Y14" s="2" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2036-07-24</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr"/>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE14" s="2" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AF14" s="2" t="inlineStr">
         <is>
-          <t>产业集团</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AG14" s="2" t="inlineStr">
         <is>
-          <t>产业集团</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AH14" s="2" t="inlineStr">
         <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AI14" s="2" t="inlineStr"/>
+          <t>房屋建设</t>
+        </is>
+      </c>
+      <c r="AI14" s="2" t="inlineStr">
+        <is>
+          <t>2031-07-24</t>
+        </is>
+      </c>
       <c r="AJ14" s="2" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -3890,7 +3908,7 @@
       </c>
       <c r="AK14" s="2" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AL14" s="2" t="inlineStr">
@@ -3900,10 +3918,12 @@
       </c>
       <c r="AM14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="AN14" s="2" t="inlineStr"/>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AN14" s="2" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3913,17 +3933,17 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>07-15 19:00</t>
+          <t>07-17 18:00</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>26成经02</t>
+          <t>26云能MTN004</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>283309.SH</t>
+          <t>102682656.IB</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -3932,39 +3952,39 @@
         </is>
       </c>
       <c r="F15" s="2" t="n">
-        <v>1.63</v>
+        <v>10</v>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.80</t>
+          <t>1.80 ~ 2.40</t>
         </is>
       </c>
       <c r="H15" s="4" t="n">
-        <v>2.29</v>
+        <v>2.14</v>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>成都经开产业投资集团有限公司</t>
+          <t>云南省能源集团有限公司</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>四川省-成都市</t>
+          <t>云南省</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>26成经01</t>
+          <t>24云能投GN001</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4.91Y</t>
+          <t>4.93Y</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2.3359</t>
+          <t>2.2567</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3974,19 +3994,19 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr"/>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>国金证券股份有限公司,华创证券有限责任公司</t>
+          <t>中国银行股份有限公司,广发证券股份有限公司</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr"/>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
@@ -3996,64 +4016,72 @@
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>成都经开产业投资集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>云南省能源集团有限公司2026年度第四期中期票据</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>2031-07-16</t>
-        </is>
-      </c>
-      <c r="Y15" s="2" t="inlineStr"/>
-      <c r="Z15" s="2" t="inlineStr"/>
+          <t>2031-07-20</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE15" s="2" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AF15" s="2" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>产业集团</t>
         </is>
       </c>
       <c r="AG15" s="2" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>产业集团</t>
         </is>
       </c>
       <c r="AH15" s="2" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AI15" s="2" t="inlineStr"/>
@@ -4074,7 +4102,7 @@
       </c>
       <c r="AM15" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="AN15" s="2" t="inlineStr"/>
@@ -4092,58 +4120,58 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>26长开03</t>
+          <t>26成经02</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>283348.SH</t>
+          <t>283309.SH</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="F16" s="2" t="n">
-        <v>6.2</v>
+        <v>1.63</v>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.30</t>
+          <t>1.80 ~ 2.80</t>
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>1.76</v>
+        <v>2.29</v>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>重庆长寿开发投资(集团)有限公司</t>
+          <t>成都经开产业投资集团有限公司</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>重庆市-长寿区</t>
+          <t>四川省-成都市</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>26长开02</t>
+          <t>26成经01</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>337D</t>
+          <t>4.91Y</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1.7167</t>
+          <t>2.3359</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -4154,7 +4182,7 @@
       <c r="P16" s="2" t="inlineStr"/>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>华源证券股份有限公司</t>
+          <t>国金证券股份有限公司,华创证券有限责任公司</t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr"/>
@@ -4175,7 +4203,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>重庆长寿开发投资(集团)有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
+          <t>成都经开产业投资集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -4185,33 +4213,29 @@
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>2027-07-18</t>
-        </is>
-      </c>
-      <c r="Y16" s="2" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2031-07-16</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr"/>
       <c r="Z16" s="2" t="inlineStr"/>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE16" s="2" t="inlineStr">
@@ -4221,12 +4245,12 @@
       </c>
       <c r="AF16" s="2" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AG16" s="2" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AH16" s="2" t="inlineStr">
@@ -4265,80 +4289,80 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>07-15 18:00</t>
+          <t>07-15 19:00</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>26华发集团MTN006</t>
+          <t>26长开03</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>102682614.IB</t>
+          <t>283348.SH</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>1Y</t>
         </is>
       </c>
       <c r="F17" s="2" t="n">
-        <v>10</v>
+        <v>6.2</v>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2.20 ~ 2.79</t>
+          <t>1.50 ~ 2.30</t>
         </is>
       </c>
       <c r="H17" s="4" t="n">
-        <v>2.79</v>
+        <v>1.76</v>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>珠海华发集团有限公司</t>
+          <t>重庆长寿开发投资(集团)有限公司</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>广东省-珠海市</t>
+          <t>重庆市-长寿区</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>26华发集团MTN005</t>
+          <t>26长开02</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2.99Y+2.00Y</t>
+          <t>337D</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2.7332</t>
+          <t>1.7167</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr"/>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>江苏银行股份有限公司,东莞银行股份有限公司</t>
+          <t>华源证券股份有限公司</t>
         </is>
       </c>
       <c r="R17" s="2" t="inlineStr"/>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -4348,68 +4372,68 @@
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>珠海华发集团有限公司2026年度第六期中期票据</t>
+          <t>重庆长寿开发投资(集团)有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>2029-07-16</t>
-        </is>
-      </c>
-      <c r="Y17" s="2" t="inlineStr"/>
-      <c r="Z17" s="2" t="inlineStr">
+          <t>2027-07-18</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr"/>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
         <is>
           <t>2026-07-17</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB17" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AE17" s="2" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AF17" s="2" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AG17" s="2" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AH17" s="2" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AI17" s="2" t="inlineStr"/>
@@ -4433,34 +4457,32 @@
           <t>2026-07-15</t>
         </is>
       </c>
-      <c r="AN17" s="2" t="n">
-        <v>0.02</v>
-      </c>
+      <c r="AN17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>07-10 19:00</t>
+          <t>07-15 18:00</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>26云能03</t>
+          <t>26华发集团MTN006</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>245651.SH</t>
+          <t>102682614.IB</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="F18" s="2" t="n">
@@ -4468,40 +4490,40 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.40</t>
+          <t>2.20 ~ 2.79</t>
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>2.05</v>
+        <v>2.79</v>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>云南省能源集团有限公司</t>
+          <t>珠海华发集团有限公司</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>云南省</t>
+          <t>广东省-珠海市</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>24云能投GN001</t>
+          <t>26华发集团MTN005</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4.95Y</t>
+          <t>2.99Y+2.00Y</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2.2717</t>
+          <t>2.7332</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
@@ -4512,13 +4534,13 @@
       <c r="P18" s="2" t="inlineStr"/>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,招商证券股份有限公司,申万宏源证券有限公司</t>
+          <t>江苏银行股份有限公司,东莞银行股份有限公司</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr"/>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
@@ -4528,12 +4550,12 @@
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>云南省能源集团有限公司2026年面向专业投资者公开发行公司债券(第三期)</t>
+          <t>珠海华发集团有限公司2026年度第六期中期票据</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -4543,14 +4565,10 @@
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>2031-07-13</t>
-        </is>
-      </c>
-      <c r="Y18" s="2" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2029-07-16</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr"/>
       <c r="Z18" s="2" t="inlineStr">
         <is>
           <t>2026-07-17</t>
@@ -4558,12 +4576,12 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -4573,7 +4591,7 @@
       </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AE18" s="2" t="inlineStr">
@@ -4583,12 +4601,12 @@
       </c>
       <c r="AF18" s="2" t="inlineStr">
         <is>
-          <t>产业集团</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AG18" s="2" t="inlineStr">
         <is>
-          <t>产业集团</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AH18" s="2" t="inlineStr">
@@ -4614,10 +4632,12 @@
       </c>
       <c r="AM18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="AN18" s="2" t="inlineStr"/>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AN18" s="2" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4627,63 +4647,63 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>07-10 18:00</t>
+          <t>07-10 19:00</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>26华发集团MTN005</t>
+          <t>26云能03</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>102682543.IB</t>
+          <t>245651.SH</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="F19" s="2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2.20 ~ 2.78</t>
+          <t>1.80 ~ 2.40</t>
         </is>
       </c>
       <c r="H19" s="4" t="n">
-        <v>2.78</v>
+        <v>2.05</v>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>珠海华发集团有限公司</t>
+          <t>云南省能源集团有限公司</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>广东省-珠海市</t>
+          <t>云南省</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>24华发集团MTN013</t>
+          <t>24云能投GN001</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3.09Y</t>
+          <t>4.95Y</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2.7518</t>
+          <t>2.2717</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -4694,13 +4714,13 @@
       <c r="P19" s="2" t="inlineStr"/>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>上海银行股份有限公司,厦门国际银行股份有限公司</t>
+          <t>国泰海通证券股份有限公司,招商证券股份有限公司,申万宏源证券有限公司</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr"/>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
@@ -4710,12 +4730,12 @@
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>珠海华发集团有限公司2026年度第五期中期票据</t>
+          <t>云南省能源集团有限公司2026年面向专业投资者公开发行公司债券(第三期)</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -4735,7 +4755,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -4755,7 +4775,7 @@
       </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE19" s="2" t="inlineStr">
@@ -4765,12 +4785,12 @@
       </c>
       <c r="AF19" s="2" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>产业集团</t>
         </is>
       </c>
       <c r="AG19" s="2" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>产业集团</t>
         </is>
       </c>
       <c r="AH19" s="2" t="inlineStr">
@@ -4778,11 +4798,7 @@
           <t>综合</t>
         </is>
       </c>
-      <c r="AI19" s="2" t="inlineStr">
-        <is>
-          <t>2029-07-13</t>
-        </is>
-      </c>
+      <c r="AI19" s="2" t="inlineStr"/>
       <c r="AJ19" s="2" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -4790,7 +4806,7 @@
       </c>
       <c r="AK19" s="2" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AL19" s="2" t="inlineStr">
@@ -4803,9 +4819,7 @@
           <t>2026-07-10</t>
         </is>
       </c>
-      <c r="AN19" s="2" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AN19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4820,79 +4834,75 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>26武汉开投PPN003</t>
+          <t>26华发集团MTN005</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>032680249.IB</t>
+          <t>102682543.IB</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="F20" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>2.20 ~ 2.78</t>
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>2.04</v>
+        <v>2.78</v>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>武汉开发投资有限公司</t>
+          <t>珠海华发集团有限公司</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>湖北省-武汉市</t>
+          <t>广东省-珠海市</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>26武开03</t>
+          <t>24华发集团MTN013</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2.80Y</t>
+          <t>3.09Y</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2.0656</t>
+          <t>2.7518</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr"/>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,兴业银行股份有限公司,渤海银行股份有限公司,广发银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>武汉金融控股(集团)有限公司</t>
-        </is>
-      </c>
+          <t>上海银行股份有限公司,厦门国际银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr"/>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -4907,74 +4917,82 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>武汉开发投资有限公司2026年度第三期定向债务融资工具</t>
+          <t>珠海华发集团有限公司2026年度第五期中期票据</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
+          <t>2031-07-13</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AD20" s="2" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="AE20" s="2" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AF20" s="2" t="inlineStr">
+        <is>
+          <t>产业控股</t>
+        </is>
+      </c>
+      <c r="AG20" s="2" t="inlineStr">
+        <is>
+          <t>产业控股</t>
+        </is>
+      </c>
+      <c r="AH20" s="2" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AI20" s="2" t="inlineStr">
+        <is>
           <t>2029-07-13</t>
         </is>
       </c>
-      <c r="Y20" s="2" t="inlineStr"/>
-      <c r="Z20" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="AB20" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="AC20" s="2" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AD20" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AE20" s="2" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AF20" s="2" t="inlineStr">
-        <is>
-          <t>产业控股</t>
-        </is>
-      </c>
-      <c r="AG20" s="2" t="inlineStr">
-        <is>
-          <t>产业控股</t>
-        </is>
-      </c>
-      <c r="AH20" s="2" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AI20" s="2" t="inlineStr"/>
       <c r="AJ20" s="2" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AK20" s="2" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AL20" s="2" t="inlineStr">
@@ -4987,7 +5005,9 @@
           <t>2026-07-10</t>
         </is>
       </c>
-      <c r="AN20" s="2" t="inlineStr"/>
+      <c r="AN20" s="2" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4997,22 +5017,22 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>07-09 18:00</t>
+          <t>07-10 18:00</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>26湖北港口MTN003</t>
+          <t>26武汉开投PPN003</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>102682535.IB</t>
+          <t>032680249.IB</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="F21" s="2" t="n">
@@ -5020,57 +5040,61 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1.85</v>
+        <v>2.04</v>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>湖北港口集团有限公司</t>
+          <t>武汉开发投资有限公司</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>湖北省</t>
+          <t>湖北省-武汉市</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>26湖北港口MTN002</t>
+          <t>26武开03</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2.67Y+N</t>
+          <t>2.80Y</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1.8352</t>
+          <t>2.0656</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr"/>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,中信银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr"/>
+          <t>国泰海通证券股份有限公司,兴业银行股份有限公司,渤海银行股份有限公司,广发银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>武汉金融控股(集团)有限公司</t>
+        </is>
+      </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
@@ -5085,35 +5109,35 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>湖北港口集团有限公司2026年度第三期中期票据</t>
+          <t>武汉开发投资有限公司2026年度第三期定向债务融资工具</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>2029-07-10</t>
+          <t>2029-07-13</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr"/>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="AB21" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
           <t>产业</t>
@@ -5121,22 +5145,22 @@
       </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE21" s="2" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AF21" s="2" t="inlineStr">
         <is>
-          <t>港口</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AG21" s="2" t="inlineStr">
         <is>
-          <t>港口</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AH21" s="2" t="inlineStr">
@@ -5147,22 +5171,22 @@
       <c r="AI21" s="2" t="inlineStr"/>
       <c r="AJ21" s="2" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AK21" s="2" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AL21" s="2" t="inlineStr">
         <is>
-          <t>次级债权</t>
+          <t>普通债权</t>
         </is>
       </c>
       <c r="AM21" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="AN21" s="2" t="inlineStr"/>
@@ -5175,80 +5199,80 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>07-07 18:00</t>
+          <t>07-09 18:00</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>26新都香城PPN003</t>
+          <t>26湖北港口MTN003</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>032680385.IB</t>
+          <t>102682535.IB</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="F22" s="2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.80</t>
+          <t>1.30 ~ 2.30</t>
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>2.18</v>
+        <v>1.85</v>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>成都市新都香城建设投资有限公司</t>
+          <t>湖北港口集团有限公司</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>四川省-成都市</t>
+          <t>湖北省</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>26新都香城PPN002</t>
+          <t>26湖北港口MTN002</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4.95Y</t>
+          <t>2.67Y+N</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2.1854</t>
+          <t>1.8352</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr"/>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>长城证券股份有限公司,成都农村商业银行股份有限公司,兴业银行股份有限公司</t>
+          <t>国泰海通证券股份有限公司,中信银行股份有限公司</t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr"/>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
@@ -5263,43 +5287,43 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>成都市新都香城建设投资有限公司2026年度第三期定向债务融资工具</t>
+          <t>湖北港口集团有限公司2026年度第三期中期票据</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>2031-07-08</t>
+          <t>2029-07-10</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr"/>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE22" s="2" t="inlineStr">
@@ -5309,12 +5333,12 @@
       </c>
       <c r="AF22" s="2" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>港口</t>
         </is>
       </c>
       <c r="AG22" s="2" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>港口</t>
         </is>
       </c>
       <c r="AH22" s="2" t="inlineStr">
@@ -5330,17 +5354,17 @@
       </c>
       <c r="AK22" s="2" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AL22" s="2" t="inlineStr">
         <is>
-          <t>普通债权</t>
+          <t>次级债权</t>
         </is>
       </c>
       <c r="AM22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="AN22" s="2" t="inlineStr"/>
@@ -5358,79 +5382,75 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>26金融街MTN003</t>
+          <t>26新都香城PPN003</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>102602112.IB</t>
+          <t>032680385.IB</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="F23" s="2" t="n">
-        <v>11.4</v>
+        <v>3</v>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>2.10 ~ 2.90</t>
+          <t>1.80 ~ 2.80</t>
         </is>
       </c>
       <c r="H23" s="4" t="n">
-        <v>2.7</v>
+        <v>2.18</v>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>金融街控股股份有限公司</t>
+          <t>成都市新都香城建设投资有限公司</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>四川省-成都市</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>24金街04</t>
+          <t>26新都香城PPN002</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2.97Y+2.00Y</t>
+          <t>4.95Y</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2.8101</t>
+          <t>2.1854</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr"/>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,南京银行股份有限公司</t>
+          <t>长城证券股份有限公司,成都农村商业银行股份有限公司,兴业银行股份有限公司</t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr"/>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -5445,12 +5465,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>金融街控股股份有限公司2026年度第三期中期票据</t>
+          <t>成都市新都香城建设投资有限公司2026年度第三期定向债务融资工具</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
@@ -5476,60 +5496,242 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AD23" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AE23" s="2" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AF23" s="2" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AG23" s="2" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AH23" s="2" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AI23" s="2" t="inlineStr"/>
+      <c r="AJ23" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AK23" s="2" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AL23" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AM23" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="AN23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>07-07 18:00</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>26金融街MTN003</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>102602112.IB</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>3+2</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>2.10 ~ 2.90</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>金融街控股股份有限公司</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>北京市</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>24金街04</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>2.97Y+2.00Y</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>2.8101</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>中信证券股份有限公司,南京银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>中期票据</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>金融街控股股份有限公司2026年度第三期中期票据</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>2031-07-08</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr"/>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
           <t>产业</t>
         </is>
       </c>
-      <c r="AD23" s="2" t="inlineStr">
+      <c r="AD24" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AE23" s="2" t="inlineStr">
+      <c r="AE24" s="2" t="inlineStr">
         <is>
           <t>房地产</t>
         </is>
       </c>
-      <c r="AF23" s="2" t="inlineStr">
+      <c r="AF24" s="2" t="inlineStr">
         <is>
           <t>房地产开发</t>
         </is>
       </c>
-      <c r="AG23" s="2" t="inlineStr">
+      <c r="AG24" s="2" t="inlineStr">
         <is>
           <t>住宅楼房</t>
         </is>
       </c>
-      <c r="AH23" s="2" t="inlineStr">
+      <c r="AH24" s="2" t="inlineStr">
         <is>
           <t>房地产开发</t>
         </is>
       </c>
-      <c r="AI23" s="2" t="inlineStr">
+      <c r="AI24" s="2" t="inlineStr">
         <is>
           <t>2029-07-08</t>
         </is>
       </c>
-      <c r="AJ23" s="2" t="inlineStr">
+      <c r="AJ24" s="2" t="inlineStr">
         <is>
           <t>无担保</t>
         </is>
       </c>
-      <c r="AK23" s="2" t="inlineStr">
+      <c r="AK24" s="2" t="inlineStr">
         <is>
           <t>含权</t>
         </is>
       </c>
-      <c r="AL23" s="2" t="inlineStr">
+      <c r="AL24" s="2" t="inlineStr">
         <is>
           <t>普通债权</t>
         </is>
       </c>
-      <c r="AM23" s="2" t="inlineStr">
+      <c r="AM24" s="2" t="inlineStr">
         <is>
           <t>2026-07-07</t>
         </is>
       </c>
-      <c r="AN23" s="2" t="inlineStr"/>
+      <c r="AN24" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
